--- a/Filtered_V3.0/COCXG_HCA_Florida_St.Lucie_Hospital.xlsx
+++ b/Filtered_V3.0/COCXG_HCA_Florida_St.Lucie_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airstrip Technologies (ONE)-Admissions </t>
+          <t>Airstrip Technologies (ONE)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,7 +1997,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2064,22 +2079,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Candescent Health/Envision Healthcare (Candescent Health)-</t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2516,7 +2516,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2538,7 +2553,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2583,7 +2598,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2620,7 +2635,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-radord</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2666,21 +2681,6 @@
       <c r="P29" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3308,7 +3308,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3330,7 +3345,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3375,22 +3390,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3606,17 +3606,17 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Admissions </t>
+          <t>GE (CPN - Gold Standard)-ADMO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Clinical Monitoring Results </t>
+          <t>GE (CPN - Gold Standard)-ITSHMRO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PCSCMI</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Monitoring Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-ITS HM Results </t>
+          <t>GE (CPN - Gold Standard)-LABRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Lab Results (Discrete) </t>
+          <t>GE (CPN - Gold Standard)-PCSCMI</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>PCSCMI</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">Clinical Monitoring Results </t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4752,6 +4752,21 @@
       <c r="P57" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4773,7 +4788,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4823,17 +4838,17 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4855,7 +4870,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4900,22 +4915,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4937,7 +4952,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5019,7 +5034,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5064,22 +5079,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5482,6 +5482,21 @@
       <c r="P67" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -5503,7 +5518,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5548,22 +5563,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5585,7 +5600,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5630,22 +5645,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5667,7 +5682,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5717,17 +5732,17 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5749,7 +5764,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-radord</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5795,21 +5810,6 @@
       <c r="P71" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>OMORDO</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6169,17 +6169,17 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6246,22 +6246,22 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6328,22 +6328,22 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6617,6 +6617,21 @@
       <c r="P82" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6638,7 +6653,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6688,17 +6703,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6735,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6770,17 +6785,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6817,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6852,7 +6867,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -6862,7 +6877,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6884,7 +6899,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6934,7 +6949,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -6944,7 +6959,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6966,7 +6981,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7016,17 +7031,17 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -7048,7 +7063,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7130,7 +7145,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7212,7 +7227,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7262,17 +7277,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7309,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7344,17 +7359,17 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7391,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7426,17 +7441,17 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7473,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7504,21 +7519,6 @@
       <c r="P93" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7648,6 +7648,21 @@
       <c r="P95" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7669,7 +7684,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7715,6 +7730,21 @@
       <c r="P96" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7766,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7786,17 +7816,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7818,7 +7848,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7868,17 +7898,17 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7930,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7982,7 +8012,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8032,7 +8062,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8042,7 +8072,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -8064,7 +8094,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8114,7 +8144,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -8124,7 +8154,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -8146,7 +8176,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8228,7 +8258,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8278,17 +8308,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -8310,7 +8340,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8360,17 +8390,17 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8422,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8474,7 +8504,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8524,17 +8554,17 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8586,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8638,7 +8668,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8688,17 +8718,17 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8750,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8770,17 +8800,17 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8832,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8852,17 +8882,17 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8914,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8934,17 +8964,17 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8996,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9016,17 +9046,17 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9078,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9094,21 +9124,6 @@
       <c r="P113" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9145,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9176,21 +9191,6 @@
       <c r="P114" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9736,7 +9736,22 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9758,7 +9773,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9825,7 +9840,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9870,22 +9885,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Care Management-Facility)-Admissions </t>
+          <t>HCA D&amp;IS (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10159,6 +10159,21 @@
       <c r="P128" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -10180,7 +10195,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10230,17 +10245,17 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10277,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10312,17 +10327,17 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10344,7 +10359,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10394,17 +10409,17 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10441,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10476,7 +10491,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -10486,7 +10501,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10508,7 +10523,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10558,7 +10573,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -10568,7 +10583,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -10590,7 +10605,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10640,17 +10655,17 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10672,7 +10687,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10722,17 +10737,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10769,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10836,7 +10851,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10918,7 +10933,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10968,17 +10983,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -11000,7 +11015,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11050,17 +11065,17 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11097,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11132,17 +11147,17 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11179,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople EDM</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11214,17 +11229,17 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11261,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Meds</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11296,17 +11311,17 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11343,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople PCS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11378,17 +11393,17 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11425,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11456,21 +11471,6 @@
       <c r="P144" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12084,6 +12084,21 @@
       <c r="P153" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -12105,7 +12120,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12155,17 +12170,17 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12202,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12237,17 +12252,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -12269,7 +12284,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12319,17 +12334,17 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12366,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12433,7 +12448,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12483,7 +12498,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -12493,7 +12508,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -12515,7 +12530,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12565,17 +12580,17 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -12597,7 +12612,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12647,17 +12662,17 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -12679,7 +12694,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12729,17 +12744,17 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -12761,7 +12776,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12816,12 +12831,12 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12858,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12893,17 +12908,17 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12925,7 +12940,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -13007,7 +13022,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13057,17 +13072,17 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -13089,7 +13104,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13139,17 +13154,17 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13186,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13221,17 +13236,17 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13268,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13303,17 +13318,17 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13350,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13381,21 +13396,6 @@
       <c r="P169" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA-CAP Division (Ancillary Dashboard)-Lab Results (Discrete) </t>
+          <t>HCA-CAP Division (Ancillary Dashboard)-LABRES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom (Navacare Patient Flow)-Admissions </t>
+          <t>Hill-Rom (Navacare Patient Flow)-ADMO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>IBM (Merge Cardio and Hemo to MPF-Patient Folder/HPF Facility)-</t>
+          <t>IBM (Merge Cardio and Hemo to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16741,6 +16741,21 @@
       <c r="P214" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16762,7 +16777,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16812,17 +16827,17 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16844,7 +16859,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16894,7 +16909,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -16904,7 +16919,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16926,7 +16941,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -16976,7 +16991,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -16986,7 +17001,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -17008,7 +17023,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17058,7 +17073,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -17068,7 +17083,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -17090,7 +17105,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17172,7 +17187,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -17222,17 +17237,17 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17254,7 +17269,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17304,17 +17319,17 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17351,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople ED Patient Visit Data</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17386,17 +17401,17 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17433,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Medication Administration</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17468,17 +17483,17 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -17500,7 +17515,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17546,21 +17561,6 @@
       <c r="P224" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17644,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">LabCorp (LabCorp)-Ref Lab Orders </t>
+          <t>LabCorp (LabCorp)-LABRR</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17689,22 +17689,22 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>LABSO</t>
+          <t>LABRR</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ref Lab Orders </t>
+          <t>Ref Lab Results</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>LabCorp (LabCorp)-Ref Lab Results</t>
+          <t>LabCorp (LabCorp)-LABSO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17771,22 +17771,22 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>LABRR</t>
+          <t>LABSO</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>Ref Lab Results</t>
+          <t xml:space="preserve">Ref Lab Orders </t>
         </is>
       </c>
     </row>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>McKesson (MPF-Patient Folder/HPF Facility to ED Billing)-</t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility to ED Billing)-bill</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18559,6 +18559,21 @@
       <c r="P238" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -18580,7 +18595,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18630,17 +18645,17 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -18662,7 +18677,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18712,7 +18727,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -18722,7 +18737,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -18744,7 +18759,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18794,7 +18809,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -18804,7 +18819,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -18826,7 +18841,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18876,7 +18891,7 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -18886,7 +18901,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -18908,7 +18923,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -18990,7 +19005,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19040,17 +19055,17 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19072,7 +19087,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19118,21 +19133,6 @@
       <c r="P245" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19832,7 +19832,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Admissions </t>
+          <t>Net Health (ReDoc Xfit)-ADMO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Charges </t>
+          <t>Net Health (ReDoc Xfit)-Patient Accounting</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (Wound Care)-Admissions </t>
+          <t>Net Health (Wound Care)-ADMO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -20818,7 +20818,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21173,7 +21173,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21363,6 +21363,21 @@
       <c r="P275" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21384,7 +21399,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21430,21 +21445,6 @@
       <c r="P276" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MD - CMORE)-Admissions </t>
+          <t>Provation (MD - CMORE to MD - CMORE)-ADMO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MD - CMORE)-Scheduling </t>
+          <t>Provation (MD - CMORE to MD - CMORE)-CWSO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21754,7 +21754,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScottCare (TeleRehab VersaCare to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>ScottCare (TeleRehab VersaCare to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siemens (RapidComm)-Admissions </t>
+          <t>Siemens (RapidComm)-ADMO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team Health (Team Health)-Admissions </t>
+          <t>Team Health (Team Health)-ADMO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Telcor (Quick-Link)-</t>
+          <t>Telcor (Quick-Link)-ADMO</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22231,7 +22231,22 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -22253,7 +22268,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telcor (Quick-Link)-Admissions </t>
+          <t>Telcor (Quick-Link)-labpoc</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22298,22 +22313,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22561,7 +22561,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22705,7 +22705,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22787,7 +22787,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telexy Healthcare Inc (Q-path to Q-path)-Admissions </t>
+          <t>Telexy Healthcare Inc (Q-path to Q-path)-ADMO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telexy Healthcare Inc (Q-path)-Admissions </t>
+          <t>Telexy Healthcare Inc (Q-path)-ADMO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -23594,7 +23594,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23922,7 +23922,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -24323,6 +24323,21 @@
       <c r="P315" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -24344,7 +24359,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24394,17 +24409,17 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -24426,7 +24441,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24508,7 +24523,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24590,7 +24605,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -24672,7 +24687,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -24722,17 +24737,17 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24769,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -24804,17 +24819,17 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -24836,7 +24851,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24886,17 +24901,17 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -24918,7 +24933,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -24968,17 +24983,17 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25015,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -25046,21 +25061,6 @@
       <c r="P324" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -25370,7 +25370,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -25534,7 +25534,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
